--- a/data/LCIs/Lai_2025/Lai_et_al-LCI_Metals-SI3_ReviewDetails.xlsx
+++ b/data/LCIs/Lai_2025/Lai_et_al-LCI_Metals-SI3_ReviewDetails.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/fasc_metal_sustainability/data/LCIs/Lai_2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{20B12EF3-9BDB-4EA5-AFD8-EB67068EA577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6A897F2-F1AA-497C-BF5A-44EBE3CAB401}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{20B12EF3-9BDB-4EA5-AFD8-EB67068EA577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A97FD070-0715-4B8D-9D9B-945E792F693F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10659,7 +10659,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="177" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B177" s="28">
         <v>28</v>
       </c>
@@ -10676,7 +10676,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="178" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B178" s="24">
         <v>28</v>
       </c>
@@ -10693,7 +10693,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="179" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B179" s="24">
         <v>28</v>
       </c>
@@ -10710,7 +10710,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="180" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B180" s="24">
         <v>28</v>
       </c>
@@ -10727,7 +10727,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="181" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B181" s="24">
         <v>28</v>
       </c>
@@ -10744,7 +10744,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="182" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B182" s="24">
         <v>28</v>
       </c>
@@ -10761,7 +10761,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="183" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B183" s="24">
         <v>28</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="184" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B184" s="24">
         <v>28</v>
       </c>
@@ -10795,7 +10795,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="185" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B185" s="24">
         <v>28</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B186" s="24">
         <v>28</v>
       </c>
@@ -10829,7 +10829,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="187" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B187" s="24">
         <v>28</v>
       </c>
@@ -10846,7 +10846,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="188" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B188" s="24">
         <v>28</v>
       </c>
@@ -10863,7 +10863,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="189" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B189" s="24">
         <v>28</v>
       </c>
@@ -10880,7 +10880,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="190" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B190" s="24">
         <v>28</v>
       </c>
@@ -10897,7 +10897,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="191" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B191" s="24">
         <v>28</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="192" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B192" s="24">
         <v>28</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="193" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B193" s="24">
         <v>28</v>
       </c>
@@ -10948,7 +10948,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="194" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B194" s="24">
         <v>28</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="195" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:6" ht="45" x14ac:dyDescent="0.25">
       <c r="B195" s="24">
         <v>28</v>
       </c>
@@ -10982,7 +10982,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="196" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B196" s="24">
         <v>28</v>
       </c>
@@ -10999,7 +10999,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="197" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:6" ht="30" x14ac:dyDescent="0.25">
       <c r="B197" s="24">
         <v>28</v>
       </c>
@@ -11016,7 +11016,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="198" spans="2:6" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B198" s="26">
         <v>28</v>
       </c>
@@ -11033,7 +11033,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="199" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B199" s="28">
         <v>29</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="200" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B200" s="24">
         <v>29</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="201" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B201" s="24">
         <v>29</v>
       </c>
@@ -11084,7 +11084,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="202" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B202" s="24">
         <v>29</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="203" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B203" s="24">
         <v>29</v>
       </c>
@@ -11118,7 +11118,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="204" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B204" s="24">
         <v>29</v>
       </c>
@@ -11135,7 +11135,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="205" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B205" s="24">
         <v>29</v>
       </c>
@@ -11152,7 +11152,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="206" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B206" s="24">
         <v>29</v>
       </c>
@@ -11169,7 +11169,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="207" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B207" s="24">
         <v>29</v>
       </c>
@@ -11186,7 +11186,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="208" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B208" s="24">
         <v>29</v>
       </c>
@@ -11203,7 +11203,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="209" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B209" s="24">
         <v>29</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="210" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B210" s="24">
         <v>29</v>
       </c>
@@ -11237,7 +11237,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="211" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B211" s="24">
         <v>29</v>
       </c>
@@ -11254,7 +11254,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="212" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B212" s="24">
         <v>29</v>
       </c>
@@ -11271,7 +11271,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="213" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B213" s="24">
         <v>29</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="214" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B214" s="24">
         <v>29</v>
       </c>
@@ -11305,7 +11305,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="215" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B215" s="24">
         <v>29</v>
       </c>
@@ -11322,7 +11322,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="216" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B216" s="24">
         <v>29</v>
       </c>
@@ -11339,7 +11339,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="217" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B217" s="24">
         <v>29</v>
       </c>
@@ -11356,7 +11356,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="218" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B218" s="24">
         <v>29</v>
       </c>
@@ -11373,7 +11373,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="219" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B219" s="24">
         <v>29</v>
       </c>
@@ -11390,7 +11390,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="220" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B220" s="24">
         <v>29</v>
       </c>
@@ -11407,7 +11407,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="221" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B221" s="24">
         <v>29</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="222" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B222" s="24">
         <v>29</v>
       </c>
@@ -11441,7 +11441,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="223" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B223" s="24">
         <v>29</v>
       </c>
@@ -11458,7 +11458,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="224" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B224" s="24">
         <v>29</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="225" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B225" s="24">
         <v>29</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="226" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B226" s="24">
         <v>29</v>
       </c>
@@ -11509,7 +11509,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="227" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B227" s="24">
         <v>29</v>
       </c>
@@ -11526,7 +11526,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="228" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B228" s="24">
         <v>29</v>
       </c>
@@ -11543,7 +11543,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="229" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B229" s="24">
         <v>29</v>
       </c>
@@ -11560,7 +11560,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="230" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B230" s="24">
         <v>29</v>
       </c>
@@ -11577,7 +11577,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="231" spans="2:6" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:6" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B231" s="24">
         <v>29</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="232" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B232" s="24">
         <v>29</v>
       </c>
@@ -11611,7 +11611,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="233" spans="2:6" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:6" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B233" s="24">
         <v>29</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="234" spans="2:6" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:6" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B234" s="24">
         <v>29</v>
       </c>
@@ -11645,7 +11645,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="235" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B235" s="24">
         <v>29</v>
       </c>
@@ -11662,7 +11662,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="236" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B236" s="24">
         <v>29</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="237" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B237" s="24">
         <v>29</v>
       </c>
@@ -11696,7 +11696,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="238" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B238" s="24">
         <v>29</v>
       </c>
@@ -11713,7 +11713,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="239" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B239" s="24">
         <v>29</v>
       </c>
@@ -11730,7 +11730,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="240" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B240" s="24">
         <v>29</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="241" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B241" s="24">
         <v>29</v>
       </c>
@@ -11764,7 +11764,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="242" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B242" s="24">
         <v>29</v>
       </c>
@@ -11781,7 +11781,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="243" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B243" s="24">
         <v>29</v>
       </c>
@@ -11798,7 +11798,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="244" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B244" s="24">
         <v>29</v>
       </c>
@@ -11815,7 +11815,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="245" spans="2:6" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="2:6" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B245" s="26">
         <v>29</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="246" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B246" s="28">
         <v>30</v>
       </c>
@@ -11849,7 +11849,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="247" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B247" s="30">
         <v>30</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="248" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B248" s="30">
         <v>30</v>
       </c>
@@ -11883,7 +11883,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="249" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B249" s="30">
         <v>30</v>
       </c>
@@ -11900,7 +11900,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="250" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B250" s="30">
         <v>30</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="251" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B251" s="30">
         <v>30</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="252" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B252" s="30">
         <v>30</v>
       </c>
@@ -11951,7 +11951,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="253" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B253" s="30">
         <v>30</v>
       </c>
@@ -11968,7 +11968,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="254" spans="2:6" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:6" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B254" s="30">
         <v>30</v>
       </c>
@@ -11985,7 +11985,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="255" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B255" s="30">
         <v>30</v>
       </c>
@@ -12002,7 +12002,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="256" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B256" s="30">
         <v>30</v>
       </c>
@@ -12019,7 +12019,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="257" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B257" s="30">
         <v>30</v>
       </c>
@@ -12036,7 +12036,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="258" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B258" s="30">
         <v>30</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="259" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B259" s="30">
         <v>30</v>
       </c>
@@ -12070,7 +12070,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="260" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B260" s="30">
         <v>30</v>
       </c>
@@ -12087,7 +12087,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="261" spans="2:6" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="2:6" ht="31.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B261" s="31">
         <v>30</v>
       </c>
@@ -12121,7 +12121,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="263" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B263" s="29">
         <v>32</v>
       </c>
@@ -12138,7 +12138,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="264" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B264" s="30">
         <v>32</v>
       </c>
@@ -12155,7 +12155,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="265" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B265" s="30">
         <v>32</v>
       </c>
@@ -12172,7 +12172,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="266" spans="2:6" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="2:6" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B266" s="31">
         <v>32</v>
       </c>
@@ -12206,7 +12206,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="268" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B268" s="28">
         <v>34</v>
       </c>
@@ -12223,7 +12223,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="269" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B269" s="24">
         <v>34</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="270" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B270" s="24">
         <v>34</v>
       </c>
@@ -12257,7 +12257,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="271" spans="2:6" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="2:6" ht="31.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B271" s="26">
         <v>34</v>
       </c>
@@ -12291,7 +12291,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="273" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B273" s="28">
         <v>40</v>
       </c>
@@ -12308,7 +12308,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="274" spans="2:6" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="2:6" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B274" s="31">
         <v>40</v>
       </c>
@@ -12325,7 +12325,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="275" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B275" s="29">
         <v>41</v>
       </c>
@@ -12342,7 +12342,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="276" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B276" s="30">
         <v>41</v>
       </c>
@@ -12359,7 +12359,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="277" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B277" s="30">
         <v>41</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="278" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B278" s="30">
         <v>41</v>
       </c>
@@ -12393,7 +12393,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="279" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B279" s="30">
         <v>41</v>
       </c>
@@ -12410,7 +12410,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="280" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B280" s="30">
         <v>41</v>
       </c>
@@ -12427,7 +12427,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="281" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B281" s="30">
         <v>41</v>
       </c>
@@ -12444,7 +12444,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="282" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B282" s="30">
         <v>41</v>
       </c>
@@ -12461,7 +12461,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="283" spans="2:6" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="2:6" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B283" s="31">
         <v>41</v>
       </c>
@@ -12478,7 +12478,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="284" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B284" s="28">
         <v>42</v>
       </c>
@@ -12495,7 +12495,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="285" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B285" s="24">
         <v>42</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="286" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B286" s="24">
         <v>42</v>
       </c>
@@ -12529,7 +12529,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="287" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B287" s="24">
         <v>42</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="288" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B288" s="24">
         <v>42</v>
       </c>
@@ -12563,7 +12563,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="289" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B289" s="24">
         <v>42</v>
       </c>
@@ -12580,7 +12580,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="290" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B290" s="24">
         <v>42</v>
       </c>
@@ -12597,7 +12597,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="291" spans="2:6" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="2:6" ht="31.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B291" s="26">
         <v>42</v>
       </c>
@@ -12614,7 +12614,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="292" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B292" s="28">
         <v>47</v>
       </c>
@@ -12631,7 +12631,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="293" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B293" s="24">
         <v>47</v>
       </c>
@@ -12648,7 +12648,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="294" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B294" s="24">
         <v>47</v>
       </c>
@@ -12665,7 +12665,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="295" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B295" s="24">
         <v>47</v>
       </c>
@@ -12682,7 +12682,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="296" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B296" s="24">
         <v>47</v>
       </c>
@@ -12699,7 +12699,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="297" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B297" s="24">
         <v>47</v>
       </c>
@@ -12716,7 +12716,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="298" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B298" s="24">
         <v>47</v>
       </c>
@@ -12733,7 +12733,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="299" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B299" s="24">
         <v>47</v>
       </c>
@@ -12750,7 +12750,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="300" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B300" s="24">
         <v>47</v>
       </c>
@@ -12767,7 +12767,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="301" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B301" s="24">
         <v>47</v>
       </c>
@@ -12784,7 +12784,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="302" spans="2:6" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="2:6" ht="31.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B302" s="26">
         <v>47</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="303" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B303" s="29">
         <v>48</v>
       </c>
@@ -12818,7 +12818,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="304" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B304" s="30">
         <v>48</v>
       </c>
@@ -12835,7 +12835,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="305" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B305" s="30">
         <v>48</v>
       </c>
@@ -12852,7 +12852,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="306" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B306" s="30">
         <v>48</v>
       </c>
@@ -12869,7 +12869,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="307" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B307" s="30">
         <v>48</v>
       </c>
@@ -12886,7 +12886,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="308" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B308" s="30">
         <v>48</v>
       </c>
@@ -12903,7 +12903,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="309" spans="2:6" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:6" ht="45.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B309" s="30">
         <v>48</v>
       </c>
@@ -12920,7 +12920,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="310" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B310" s="30">
         <v>48</v>
       </c>
@@ -12937,7 +12937,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="311" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B311" s="30">
         <v>48</v>
       </c>
@@ -12954,7 +12954,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="312" spans="2:6" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="2:6" ht="31.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B312" s="31">
         <v>48</v>
       </c>
@@ -12971,7 +12971,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="313" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B313" s="29">
         <v>49</v>
       </c>
@@ -12988,7 +12988,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="314" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B314" s="30">
         <v>49</v>
       </c>
@@ -13005,7 +13005,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="315" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B315" s="30">
         <v>49</v>
       </c>
@@ -13022,7 +13022,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="316" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B316" s="30">
         <v>49</v>
       </c>
@@ -13039,7 +13039,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="317" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B317" s="30">
         <v>49</v>
       </c>
@@ -13056,7 +13056,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="318" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B318" s="30">
         <v>49</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="319" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B319" s="30">
         <v>49</v>
       </c>
@@ -13090,7 +13090,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="320" spans="2:6" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="2:6" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B320" s="31">
         <v>49</v>
       </c>
@@ -13107,7 +13107,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="321" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B321" s="29">
         <v>50</v>
       </c>
@@ -13124,7 +13124,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="322" spans="2:6" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="2:6" ht="31.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B322" s="31">
         <v>50</v>
       </c>
@@ -13141,7 +13141,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="323" spans="2:6" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:6" ht="60.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B323" s="29">
         <v>51</v>
       </c>
@@ -13158,7 +13158,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="324" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B324" s="30">
         <v>51</v>
       </c>
@@ -13175,7 +13175,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="325" spans="2:6" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="2:6" ht="31.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B325" s="31">
         <v>51</v>
       </c>
@@ -13192,7 +13192,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="326" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B326" s="28">
         <v>52</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="327" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B327" s="24">
         <v>52</v>
       </c>
@@ -13226,7 +13226,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="328" spans="2:6" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="2:6" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B328" s="26">
         <v>52</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="329" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B329" s="29">
         <v>56</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="330" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B330" s="30">
         <v>56</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="331" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B331" s="30">
         <v>56</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="332" spans="2:6" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="2:6" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B332" s="31">
         <v>56</v>
       </c>
@@ -13328,7 +13328,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="334" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B334" s="29">
         <v>74</v>
       </c>
@@ -13345,7 +13345,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="335" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B335" s="30">
         <v>74</v>
       </c>
@@ -13362,7 +13362,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="336" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B336" s="30">
         <v>74</v>
       </c>
@@ -13379,7 +13379,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="337" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B337" s="30">
         <v>74</v>
       </c>
@@ -13396,7 +13396,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="338" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B338" s="30">
         <v>74</v>
       </c>
@@ -13413,7 +13413,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="339" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B339" s="30">
         <v>74</v>
       </c>
@@ -13430,7 +13430,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="340" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B340" s="30">
         <v>74</v>
       </c>
@@ -13447,7 +13447,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="341" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B341" s="30">
         <v>74</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="342" spans="2:6" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="2:6" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B342" s="31">
         <v>74</v>
       </c>
@@ -13481,7 +13481,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="343" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B343" s="29">
         <v>79</v>
       </c>
@@ -13498,7 +13498,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="344" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B344" s="30">
         <v>79</v>
       </c>
@@ -13515,7 +13515,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="345" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B345" s="30">
         <v>79</v>
       </c>
@@ -13532,7 +13532,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="346" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B346" s="30">
         <v>79</v>
       </c>
@@ -13549,7 +13549,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="347" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B347" s="30">
         <v>79</v>
       </c>
@@ -13566,7 +13566,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="348" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B348" s="30">
         <v>79</v>
       </c>
@@ -13583,7 +13583,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="349" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B349" s="30">
         <v>79</v>
       </c>
@@ -13600,7 +13600,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="350" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B350" s="30">
         <v>79</v>
       </c>
@@ -13617,7 +13617,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="351" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B351" s="30">
         <v>79</v>
       </c>
@@ -13634,7 +13634,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="352" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B352" s="30">
         <v>79</v>
       </c>
@@ -13651,7 +13651,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="353" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B353" s="30">
         <v>79</v>
       </c>
@@ -13668,7 +13668,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="354" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B354" s="30">
         <v>79</v>
       </c>
@@ -13685,7 +13685,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="355" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B355" s="30">
         <v>79</v>
       </c>
@@ -13702,7 +13702,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="356" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B356" s="30">
         <v>79</v>
       </c>
@@ -13719,7 +13719,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="357" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B357" s="30">
         <v>79</v>
       </c>
@@ -13736,7 +13736,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="358" spans="2:6" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="2:6" ht="31.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B358" s="31">
         <v>79</v>
       </c>
@@ -14314,7 +14314,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="392" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B392" s="30" t="s">
         <v>871</v>
       </c>
@@ -14331,7 +14331,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="393" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B393" s="30" t="s">
         <v>871</v>
       </c>
@@ -14348,7 +14348,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="394" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B394" s="30" t="s">
         <v>871</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="395" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B395" s="30" t="s">
         <v>871</v>
       </c>
@@ -14382,7 +14382,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="396" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B396" s="30" t="s">
         <v>871</v>
       </c>
@@ -14399,7 +14399,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="397" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B397" s="30" t="s">
         <v>871</v>
       </c>
@@ -14416,7 +14416,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="398" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B398" s="30" t="s">
         <v>871</v>
       </c>
@@ -14433,7 +14433,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="399" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B399" s="30" t="s">
         <v>871</v>
       </c>
@@ -14450,7 +14450,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="400" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B400" s="30" t="s">
         <v>871</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="401" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B401" s="30" t="s">
         <v>871</v>
       </c>
@@ -14484,7 +14484,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="402" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B402" s="30" t="s">
         <v>871</v>
       </c>
@@ -14501,7 +14501,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="403" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B403" s="30" t="s">
         <v>871</v>
       </c>
@@ -14518,7 +14518,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="404" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B404" s="30" t="s">
         <v>871</v>
       </c>
@@ -14535,7 +14535,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="405" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B405" s="30" t="s">
         <v>871</v>
       </c>
@@ -14552,7 +14552,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="406" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B406" s="30" t="s">
         <v>871</v>
       </c>
@@ -14569,7 +14569,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="407" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B407" s="30" t="s">
         <v>871</v>
       </c>
@@ -14586,7 +14586,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="408" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B408" s="30" t="s">
         <v>871</v>
       </c>
@@ -14603,7 +14603,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="409" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B409" s="30" t="s">
         <v>871</v>
       </c>
@@ -14620,7 +14620,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="410" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B410" s="30" t="s">
         <v>871</v>
       </c>
@@ -14637,7 +14637,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="411" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B411" s="30" t="s">
         <v>871</v>
       </c>
@@ -14654,7 +14654,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="412" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B412" s="30" t="s">
         <v>871</v>
       </c>
@@ -14671,7 +14671,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="413" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B413" s="30" t="s">
         <v>871</v>
       </c>
@@ -14688,7 +14688,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="414" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B414" s="30" t="s">
         <v>871</v>
       </c>
@@ -14705,7 +14705,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="415" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B415" s="30" t="s">
         <v>871</v>
       </c>
@@ -14722,7 +14722,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="416" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B416" s="30" t="s">
         <v>871</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="417" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B417" s="30" t="s">
         <v>871</v>
       </c>
@@ -14756,7 +14756,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="418" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B418" s="30" t="s">
         <v>871</v>
       </c>
@@ -14773,7 +14773,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="419" spans="2:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:6" ht="30.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B419" s="30" t="s">
         <v>871</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="420" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B420" s="30" t="s">
         <v>871</v>
       </c>
@@ -14807,7 +14807,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="421" spans="2:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B421" s="30" t="s">
         <v>871</v>
       </c>
@@ -14824,22 +14824,22 @@
         <v>958</v>
       </c>
     </row>
-    <row r="422" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="423" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="424" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="425" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="426" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="427" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="428" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="429" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="430" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="431" spans="2:6" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="422" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="423" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="424" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="425" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="426" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="427" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="428" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="429" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="430" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="431" spans="2:6" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="432" spans="2:6" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <autoFilter ref="B2:F431" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Gold (Au)"/>
+        <filter val="Nickel (Ni)"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B343:F358">
@@ -21280,7 +21280,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="203" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B203" s="24">
         <v>6</v>
       </c>
@@ -21326,7 +21326,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="205" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:8" ht="30" x14ac:dyDescent="0.25">
       <c r="B205" s="24">
         <v>6</v>
       </c>
@@ -26179,7 +26179,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="416" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B416" s="29" t="s">
         <v>871</v>
       </c>
@@ -26202,7 +26202,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="417" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B417" s="30" t="s">
         <v>871</v>
       </c>
@@ -26271,7 +26271,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="420" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B420" s="30" t="s">
         <v>871</v>
       </c>
@@ -26294,7 +26294,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="421" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B421" s="30" t="s">
         <v>871</v>
       </c>
@@ -26317,7 +26317,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="422" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B422" s="30" t="s">
         <v>871</v>
       </c>
@@ -26340,7 +26340,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="423" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="2:8" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B423" s="31" t="s">
         <v>871</v>
       </c>
@@ -26363,7 +26363,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="424" spans="2:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B424" s="29" t="s">
         <v>871</v>
       </c>
@@ -26386,7 +26386,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="425" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="2:8" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B425" s="31" t="s">
         <v>871</v>
       </c>
@@ -26409,7 +26409,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="426" spans="2:8" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B426" s="29" t="s">
         <v>871</v>
       </c>
@@ -26432,7 +26432,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="427" spans="2:8" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B427" s="30" t="s">
         <v>871</v>
       </c>
@@ -26455,7 +26455,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="428" spans="2:8" ht="31.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="2:8" ht="30.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B428" s="31" t="s">
         <v>871</v>
       </c>
@@ -26478,7 +26478,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="429" spans="2:8" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B429" s="29" t="s">
         <v>871</v>
       </c>
@@ -26501,7 +26501,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="430" spans="2:8" ht="15.75" hidden="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="B430" s="30" t="s">
         <v>871</v>
       </c>
@@ -26524,7 +26524,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="431" spans="2:8" ht="16.5" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="2:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B431" s="31" t="s">
         <v>871</v>
       </c>
@@ -26547,7 +26547,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="432" spans="2:8" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B432" s="29" t="s">
         <v>871</v>
       </c>
@@ -26662,7 +26662,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="437" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:8" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B437" s="29" t="s">
         <v>871</v>
       </c>
@@ -29058,7 +29058,7 @@
   <autoFilter ref="B2:H540" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Rare Earths (RE)"/>
+        <filter val="Graphite (C)"/>
       </filters>
     </filterColumn>
     <filterColumn colId="5">
@@ -36231,26 +36231,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004741122952C13D46BBBC92EEAE11CF32" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="d96b5fa62e5213e7d24e66b2bac0c378">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="d78c010b-218d-4be4-b2d9-423b1f51aae5" xmlns:ns3="adc0c41a-12c1-4165-8422-5f5ca88e9f6a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c2e8fc9a9c70fab2c0f7259df75af726" ns2:_="" ns3:_="">
     <xsd:import namespace="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
@@ -36473,26 +36453,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04103A44-3975-4943-AB28-65011B7E4D07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
-    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFF52A7D-629D-43DA-A27A-26245A010B40}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="d78c010b-218d-4be4-b2d9-423b1f51aae5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E87AE39D-0990-44CA-A7B1-29F47F7A9F83}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36509,4 +36490,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFF52A7D-629D-43DA-A27A-26245A010B40}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04103A44-3975-4943-AB28-65011B7E4D07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="adc0c41a-12c1-4165-8422-5f5ca88e9f6a"/>
+    <ds:schemaRef ds:uri="d78c010b-218d-4be4-b2d9-423b1f51aae5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>